--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios131.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios131.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -463,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.28398775755517</v>
+        <v>32.56239267724177</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.10231318710406</v>
+        <v>25.48178210623524</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.34785721059504</v>
+        <v>29.43849963604183</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.74465484463277</v>
+        <v>29.29645522319228</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.45239742325531</v>
+        <v>32.39363064879398</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.79448812401252</v>
+        <v>33.63595089475974</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>33.79653396104727</v>
+        <v>28.42224569493365</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.0675452554503</v>
+        <v>25.87068367024295</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.67883295990916</v>
+        <v>22.34010353177706</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.0270918483163</v>
+        <v>25.32617716167413</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38.82966186072179</v>
+        <v>29.63577319812008</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30.30854326035544</v>
+        <v>27.56455071176566</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.37835789358706</v>
+        <v>29.86620839916147</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24.97429983144605</v>
+        <v>29.9384535202496</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.91763918734134</v>
+        <v>26.0958222345524</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.11521275161741</v>
+        <v>32.19346629673936</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.343111720805</v>
+        <v>28.94788983672876</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.56835581578299</v>
+        <v>36.66493645068498</v>
       </c>
     </row>
   </sheetData>
